--- a/etc/hebrew/particles.xlsx
+++ b/etc/hebrew/particles.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -563,6 +563,90 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>there is no; there are no</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>אֵין</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>particle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>there is; there are</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>יֵשׁ</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>particle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>וְ</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>conjunction</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>direct object marker</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>אֶת</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>particle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/particles.xlsx
+++ b/etc/hebrew/particles.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,27 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>the; definite article</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>הַ־</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/particles.xlsx
+++ b/etc/hebrew/particles.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -668,6 +668,27 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>because</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>כִּי</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>conjunction</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/particles.xlsx
+++ b/etc/hebrew/particles.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -689,6 +689,27 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>because; since (formal)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>מִפְּנֵי שֶׁ־</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>conjunction</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/particles.xlsx
+++ b/etc/hebrew/particles.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -710,6 +710,27 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>if</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>אִם</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>particle; conjunction</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
